--- a/Sufficient data WITH_PO/B081JDLX48_fallback_WITH_PO.xlsx
+++ b/Sufficient data WITH_PO/B081JDLX48_fallback_WITH_PO.xlsx
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
